--- a/public/contract_upload_template.xlsx
+++ b/public/contract_upload_template.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج الرفع" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التعليمات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="القوائم" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'نموذج الرفع'!$A$1:$F$501</definedName>
+    <definedName name="RegionsList">'القوائم'!$A$2:$A$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'نموذج الرفع'!$A$1:$F$1000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +42,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000B2140"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00173F73"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -91,6 +98,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,40 +477,40 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>رقم الموظف</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>اسم الموظف</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>رقم معاملة التعيين</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>رقم معاملة الانقطاع أو اتخاذ الإجراء</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>الإقليم</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>تاريخ المباشرة</t>
         </is>
@@ -4516,16 +4532,23 @@
           <t>TX-00001</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
           <t>الرياض</t>
         </is>
       </c>
-      <c r="F502" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F501"/>
+  <autoFilter ref="A1:F1000"/>
+  <dataValidations count="2">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="إقليم غير معتمد" error="اختر الإقليم من القائمة." promptTitle="الإقليم" prompt="اختر الإقليم من القائمة المنسدلة." type="list">
+      <formula1>=RegionsList</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="أدخل تاريخًا صحيحًا." type="date" operator="between">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4543,42 +4566,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>نموذج رفع المعاملات — Contract Control</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>استخدم ورقة «نموذج الرفع» فقط لإدخال البيانات.</t>
+          <t>اختر الإقليم من القائمة المنسدلة في عمود «الإقليم». لا تكتب اسم الإقليم يدويًا.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>الحقول الإلزامية: رقم الموظف، اسم الموظف، رقم معاملة التعيين، الإقليم، تاريخ المباشرة.</t>
+          <t>تأكد من صحة رقم الموظف واسم الموظف ورقم معاملة التعيين.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>رقم معاملة الانقطاع أو اتخاذ الإجراء يترك فارغاً إذا لم يوجد.</t>
+          <t>رقم معاملة الانقطاع أو اتخاذ الإجراء يُعبأ عند الحاجة فقط.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>التاريخ يقبل dd/mm/yyyy أو yyyy-mm-dd.</t>
+          <t>تاريخ المباشرة يجب أن يكون بصيغة تاريخ Excel.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>لا تغيّر أسماء الأعمدة.</t>
         </is>
@@ -4594,4 +4617,116 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الأقاليم</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>مكة المكرمة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>المدينة المنورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>القصيم</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>المنطقة الشرقية</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>عسير</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>تبوك</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>حائل</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>الحدود الشمالية</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>نجران</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>الباحة</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>الجوف</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/contract_upload_template.xlsx
+++ b/public/contract_upload_template.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج الرفع" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="رفع العقود" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التعليمات" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="القوائم" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="RegionsList">'القوائم'!$A$2:$A$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'نموذج الرفع'!$A$1:$F$1000</definedName>
+    <definedName name="ContractRegions">'القوائم'!$A$1:$A$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'رفع العقود'!$A$1:$E$2000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,11 +477,11 @@
   <dimension ref="A1:F502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4539,13 +4540,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1000"/>
+  <autoFilter ref="A1:E2000"/>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="إقليم غير معتمد" error="اختر الإقليم من القائمة." promptTitle="الإقليم" prompt="اختر الإقليم من القائمة المنسدلة." type="list">
-      <formula1>=RegionsList</formula1>
+    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="إقليم غير صالح" error="اختر الإقليم من القائمة فقط." promptTitle="الإقليم" prompt="اختر الإقليم من القائمة المنسدلة." type="list">
+      <formula1>=ContractRegions</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="أدخل تاريخًا صحيحًا." type="date" operator="between">
-      <formula1>DATE(2000,1,1)</formula1>
+    <dataValidation sqref="E2:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="تاريخ غير صالح" error="أدخل تاريخًا صحيحًا." type="date" operator="between">
+      <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
   </dataValidations>
@@ -4625,102 +4626,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الأقاليم</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
           <t>الرياض</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>مكة المكرمة</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>المدينة المنورة</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>القصيم</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>المنطقة الشرقية</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>عسير</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>تبوك</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>حائل</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>الحدود الشمالية</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>جازان</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>نجران</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>الباحة</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>الجوف</t>
         </is>

--- a/public/contract_upload_template.xlsx
+++ b/public/contract_upload_template.xlsx
@@ -477,11 +477,11 @@
   <dimension ref="A1:F502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4542,10 +4542,10 @@
   </sheetData>
   <autoFilter ref="A1:E2000"/>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="إقليم غير صالح" error="اختر الإقليم من القائمة فقط." promptTitle="الإقليم" prompt="اختر الإقليم من القائمة المنسدلة." type="list">
+    <dataValidation sqref="E2:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="إقليم غير صالح" error="اختر الإقليم من القائمة فقط." promptTitle="الإقليم" prompt="اختر الإقليم من القائمة المنسدلة." type="list">
       <formula1>=ContractRegions</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="تاريخ غير صالح" error="أدخل تاريخًا صحيحًا." type="date" operator="between">
+    <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="تاريخ غير صالح" error="أدخل تاريخًا صحيحًا." type="date" operator="between">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>

--- a/public/contract_upload_template.xlsx
+++ b/public/contract_upload_template.xlsx
@@ -477,11 +477,11 @@
   <dimension ref="A1:F502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4542,10 +4542,10 @@
   </sheetData>
   <autoFilter ref="A1:E2000"/>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="إقليم غير صالح" error="اختر الإقليم من القائمة فقط." promptTitle="الإقليم" prompt="اختر الإقليم من القائمة المنسدلة." type="list">
+    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="إقليم غير صالح" error="اختر الإقليم من القائمة فقط." promptTitle="الإقليم" prompt="اختر الإقليم من القائمة المنسدلة." type="list">
       <formula1>=ContractRegions</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="تاريخ غير صالح" error="أدخل تاريخًا صحيحًا." type="date" operator="between">
+    <dataValidation sqref="E2:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="تاريخ غير صالح" error="أدخل تاريخًا صحيحًا." type="date" operator="between">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>

--- a/public/contract_upload_template.xlsx
+++ b/public/contract_upload_template.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="رفع المعاملات" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التعليمات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعليمات" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'رفع المعاملات'!$A$1:$E$1000</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,14 +30,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000E1C30"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,7 +60,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -420,15 +428,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,29 +456,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>رقم معاملة الانقطاع أو اتخاذ الإجراء</t>
+          <t>المسؤول</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>المسؤول</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>تاريخ المباشرة</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -482,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -491,42 +486,21 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>نموذج رفع المعاملات — Contract Control V20.0.0</t>
+          <t>نموذج رفع المعاملات — V20.1.0</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>لا يوجد إقليم في هذا النموذج. كل معاملة ترتبط مباشرة بالمستخدم المسؤول.</t>
+          <t>استخدم زر «تحميل نموذج Excel» من داخل النظام للحصول على قائمة منسدلة محدثة بأسماء جميع المستخدمين النشطين بدور مسؤول.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>عمود «المسؤول»: اكتب اسم المسؤول كما يظهر في النظام أو اسم المستخدم الخاص به.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>إذا كان الاسم غير موجود أو الحساب غير نشط فسيتم رفض الصف مع توضيح السبب.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>رقم معاملة الانقطاع أو اتخاذ الإجراء يُعبأ عند الحاجة فقط.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>تاريخ المباشرة يجب أن يكون بصيغة تاريخ Excel.</t>
+          <t>لا يوجد في هذا النموذج رقم معاملة الانقطاع أو اتخاذ الإجراء؛ يضاف فقط عند تسجيل حالة منسحب الموظف داخل المعاملة.</t>
         </is>
       </c>
     </row>
